--- a/docs/example/example-report.xlsx
+++ b/docs/example/example-report.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Сводка" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Фирмы'!$A$1:$Q$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Фирмы'!$A$1:$R$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -522,14 +522,15 @@
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -580,40 +581,45 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Что с сайтом</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Соцсети и мессенджеры</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Рейтинг</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Оценок</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Режим работы</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Источники</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Ссылка · 2ГИС</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Ссылка · Яндекс Карты</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Координаты</t>
         </is>
@@ -655,30 +661,31 @@
       </c>
       <c r="H2" s="5" t="n"/>
       <c r="I2" s="5" t="n"/>
-      <c r="J2" s="6" t="n"/>
-      <c r="K2" s="3" t="n">
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="6" t="n"/>
+      <c r="L2" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="L2" s="3" t="n">
+      <c r="M2" s="3" t="n">
         <v>3024</v>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>ежедневно, 08:00–22:00</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>Яндекс Карты</t>
         </is>
       </c>
-      <c r="O2" s="3" t="n"/>
-      <c r="P2" s="7" t="inlineStr">
+      <c r="P2" s="3" t="n"/>
+      <c r="Q2" s="7" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
       </c>
-      <c r="Q2" s="5" t="inlineStr">
+      <c r="R2" s="5" t="inlineStr">
         <is>
           <t>57.15, 65.54</t>
         </is>
@@ -716,26 +723,27 @@
       <c r="G3" s="5" t="n"/>
       <c r="H3" s="5" t="n"/>
       <c r="I3" s="5" t="n"/>
-      <c r="J3" s="6" t="n"/>
-      <c r="K3" s="3" t="n">
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="6" t="n"/>
+      <c r="L3" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="M3" s="3" t="n">
         <v>1676</v>
       </c>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>2ГИС</t>
         </is>
       </c>
-      <c r="O3" s="7" t="inlineStr">
+      <c r="P3" s="7" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
       </c>
-      <c r="P3" s="3" t="n"/>
-      <c r="Q3" s="5" t="inlineStr">
+      <c r="Q3" s="3" t="n"/>
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>57.154, 65.536</t>
         </is>
@@ -777,40 +785,41 @@
           <t>https://ola-ola.ru</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>ВКонтакте: https://vk.com/club000000001
 WhatsApp: https://wa.me/79000000001
 Telegram: https://t.me/olaola</t>
         </is>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="L4" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="M4" s="3" t="n">
         <v>255</v>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Пн–Пт 09:00–22:00, Сб–Вс 10:00–18:00</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>2ГИС, Яндекс Карты</t>
         </is>
       </c>
-      <c r="O4" s="7" t="inlineStr">
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
       </c>
-      <c r="P4" s="7" t="inlineStr">
+      <c r="Q4" s="7" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
       </c>
-      <c r="Q4" s="5" t="inlineStr">
+      <c r="R4" s="5" t="inlineStr">
         <is>
           <t>57.152187, 65.554535</t>
         </is>
@@ -848,33 +857,34 @@
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="n"/>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="3" t="n">
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="M5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="M5" s="2" t="n"/>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>2ГИС</t>
         </is>
       </c>
-      <c r="O5" s="7" t="inlineStr">
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
       </c>
-      <c r="P5" s="3" t="n"/>
-      <c r="Q5" s="5" t="inlineStr">
+      <c r="Q5" s="3" t="n"/>
+      <c r="R5" s="5" t="inlineStr">
         <is>
           <t>57.153997, 65.535134</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q5"/>
+  <autoFilter ref="A1:R5"/>
   <conditionalFormatting sqref="C2:C5">
     <cfRule type="colorScale" priority="1">
       <colorScale>
@@ -888,11 +898,11 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -966,7 +976,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>25.10.2026 02:29</t>
+          <t>25.10.2026 17:44</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1186,7 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>0–100: чем больше пробелов, тем выше. 0 — связаться не с кем</t>
+          <t>0–100: чем больше пробелов, тем выше. 0 — либо всё на месте, либо связаться не с кем</t>
         </is>
       </c>
     </row>

--- a/docs/example/example-report.xlsx
+++ b/docs/example/example-report.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Сводка" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Фирмы'!$A$1:$R$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Фирмы'!$A$1:$V$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -520,17 +520,21 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="32" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -571,55 +575,75 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Мобильный</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Почта</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Что с сайтом</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Соцсети и мессенджеры</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Рейтинг</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Оценок</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Режим работы</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Сеть</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ИНН</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>В реестре с</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Источники</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Ссылка · 2ГИС</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Ссылка · Яндекс Карты</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Координаты</t>
         </is>
@@ -659,33 +683,41 @@
           <t>+7 (900) 000-00-02</t>
         </is>
       </c>
-      <c r="H2" s="5" t="n"/>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>+7 (900) 000-00-02</t>
+        </is>
+      </c>
       <c r="I2" s="5" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="6" t="n"/>
-      <c r="L2" s="3" t="n">
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="6" t="n"/>
+      <c r="M2" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="M2" s="3" t="n">
+      <c r="N2" s="3" t="n">
         <v>3024</v>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>ежедневно, 08:00–22:00</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="5" t="n"/>
+      <c r="R2" s="3" t="n"/>
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <t>Яндекс Карты</t>
         </is>
       </c>
-      <c r="P2" s="3" t="n"/>
-      <c r="Q2" s="7" t="inlineStr">
+      <c r="T2" s="3" t="n"/>
+      <c r="U2" s="7" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
       </c>
-      <c r="R2" s="5" t="inlineStr">
+      <c r="V2" s="5" t="inlineStr">
         <is>
           <t>57.15, 65.54</t>
         </is>
@@ -723,27 +755,31 @@
       <c r="G3" s="5" t="n"/>
       <c r="H3" s="5" t="n"/>
       <c r="I3" s="5" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="6" t="n"/>
-      <c r="L3" s="3" t="n">
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="6" t="n"/>
+      <c r="M3" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="M3" s="3" t="n">
+      <c r="N3" s="3" t="n">
         <v>1676</v>
       </c>
-      <c r="N3" s="2" t="n"/>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="5" t="n"/>
+      <c r="R3" s="3" t="n"/>
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>2ГИС</t>
         </is>
       </c>
-      <c r="P3" s="7" t="inlineStr">
+      <c r="T3" s="7" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="n"/>
-      <c r="R3" s="5" t="inlineStr">
+      <c r="U3" s="3" t="n"/>
+      <c r="V3" s="5" t="inlineStr">
         <is>
           <t>57.154, 65.536</t>
         </is>
@@ -775,51 +811,55 @@
           <t>+7 (345) 266-67-07</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>ola.ola@mail.ru</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>https://ola-ola.ru</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>ВКонтакте: https://vk.com/club000000001
 WhatsApp: https://wa.me/79000000001
 Telegram: https://t.me/olaola</t>
         </is>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="M4" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="N4" s="3" t="n">
         <v>255</v>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Пн–Пт 09:00–22:00, Сб–Вс 10:00–18:00</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="P4" s="2" t="n"/>
+      <c r="Q4" s="5" t="n"/>
+      <c r="R4" s="3" t="n"/>
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t>2ГИС, Яндекс Карты</t>
         </is>
       </c>
-      <c r="P4" s="7" t="inlineStr">
+      <c r="T4" s="7" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
       </c>
-      <c r="Q4" s="7" t="inlineStr">
+      <c r="U4" s="7" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
       </c>
-      <c r="R4" s="5" t="inlineStr">
+      <c r="V4" s="5" t="inlineStr">
         <is>
           <t>57.152187, 65.554535</t>
         </is>
@@ -857,34 +897,38 @@
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="n"/>
-      <c r="J5" s="2" t="n"/>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="3" t="n">
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="6" t="n"/>
+      <c r="M5" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="N5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="N5" s="2" t="n"/>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O5" s="2" t="n"/>
+      <c r="P5" s="2" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="3" t="n"/>
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>2ГИС</t>
         </is>
       </c>
-      <c r="P5" s="7" t="inlineStr">
+      <c r="T5" s="7" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="n"/>
-      <c r="R5" s="5" t="inlineStr">
+      <c r="U5" s="3" t="n"/>
+      <c r="V5" s="5" t="inlineStr">
         <is>
           <t>57.153997, 65.535134</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R5"/>
+  <autoFilter ref="A1:V5"/>
   <conditionalFormatting sqref="C2:C5">
     <cfRule type="colorScale" priority="1">
       <colorScale>
@@ -898,11 +942,11 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T5" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -936,7 +980,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>версия 0.1.0</t>
+          <t>версия 0.2.0</t>
         </is>
       </c>
     </row>
@@ -976,7 +1020,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>25.10.2026 17:44</t>
+          <t>25.10.2026 22:33</t>
         </is>
       </c>
     </row>
